--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F321"/>
+  <dimension ref="A1:F322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10060,6 +10060,36 @@
         </is>
       </c>
     </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>3105.776374</v>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:22:34-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F322"/>
+  <dimension ref="A1:F323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10090,6 +10090,36 @@
         </is>
       </c>
     </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>3085.366679</v>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>2026-09-14T14:15:28-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F323"/>
+  <dimension ref="A1:F324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10120,6 +10120,36 @@
         </is>
       </c>
     </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>3078.939055</v>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>2026-09-15T13:06:53-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F324"/>
+  <dimension ref="A1:F325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10150,6 +10150,36 @@
         </is>
       </c>
     </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>3103.999022</v>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>2026-09-16T13:07:52-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F325"/>
+  <dimension ref="A1:F326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10180,6 +10180,36 @@
         </is>
       </c>
     </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>3114.012529</v>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>2026-09-17T13:08:28-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F326"/>
+  <dimension ref="A1:F327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10210,6 +10210,36 @@
         </is>
       </c>
     </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>3128.800779</v>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:38:13-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F327"/>
+  <dimension ref="A1:F328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10240,6 +10240,36 @@
         </is>
       </c>
     </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>3127.64036</v>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>2026-09-19T12:11:32-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F328"/>
+  <dimension ref="A1:F329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10270,6 +10270,36 @@
         </is>
       </c>
     </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>3140.322314</v>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>2026-09-20T12:24:34-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F329"/>
+  <dimension ref="A1:F330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10300,6 +10300,36 @@
         </is>
       </c>
     </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>3165.609107</v>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:18:27-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F330"/>
+  <dimension ref="A1:F331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10330,6 +10330,36 @@
         </is>
       </c>
     </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>3173.060103</v>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>2026-09-22T13:02:11-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F331"/>
+  <dimension ref="A1:F332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10360,6 +10360,36 @@
         </is>
       </c>
     </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>3200.183068</v>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>2026-09-23T13:21:24-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F332"/>
+  <dimension ref="A1:F333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10390,6 +10390,36 @@
         </is>
       </c>
     </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>3202.804058</v>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>2026-09-24T13:23:11-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F333"/>
+  <dimension ref="A1:F334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10420,6 +10420,36 @@
         </is>
       </c>
     </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>3264.540762</v>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>2026-09-25T13:29:23-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F334"/>
+  <dimension ref="A1:F335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10450,6 +10450,36 @@
         </is>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>3256.240909</v>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>2026-09-26T12:43:28-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F335"/>
+  <dimension ref="A1:F336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10480,6 +10480,36 @@
         </is>
       </c>
     </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>3257.14796</v>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>2026-09-27T13:16:45-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F336"/>
+  <dimension ref="A1:F337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10510,6 +10510,36 @@
         </is>
       </c>
     </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D337" t="n">
+        <v>3334.28191</v>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>2026-09-28T15:30:15-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F337"/>
+  <dimension ref="A1:F338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10540,6 +10540,36 @@
         </is>
       </c>
     </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>3300.866532</v>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>2026-09-29T14:18:59-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F338"/>
+  <dimension ref="A1:F339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10570,6 +10570,36 @@
         </is>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D339" t="n">
+        <v>3366.901593</v>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>2026-09-30T14:07:25-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F339"/>
+  <dimension ref="A1:F340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10600,6 +10600,36 @@
         </is>
       </c>
     </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D340" t="n">
+        <v>3333.963413</v>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>2026-10-01T14:27:17-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F340"/>
+  <dimension ref="A1:F341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10630,6 +10630,36 @@
         </is>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D341" t="n">
+        <v>3308.229231</v>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>2026-10-02T14:10:39-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F341"/>
+  <dimension ref="A1:F342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10660,6 +10660,36 @@
         </is>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D342" t="n">
+        <v>3311.925714</v>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>2026-10-03T12:53:08-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F342"/>
+  <dimension ref="A1:F343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10690,6 +10690,36 @@
         </is>
       </c>
     </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D343" t="n">
+        <v>3311.644334</v>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>2026-10-04T13:05:25-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F343"/>
+  <dimension ref="A1:F344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10720,6 +10720,36 @@
         </is>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>3308.762446</v>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>2026-10-05T16:26:56-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F344"/>
+  <dimension ref="A1:F345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10750,6 +10750,36 @@
         </is>
       </c>
     </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D345" t="n">
+        <v>3286.004945</v>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>2026-10-06T14:26:56-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F345"/>
+  <dimension ref="A1:F346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10780,6 +10780,36 @@
         </is>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>3199.575723</v>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>2026-10-07T14:53:44-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F346"/>
+  <dimension ref="A1:F347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10810,6 +10810,36 @@
         </is>
       </c>
     </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D347" t="n">
+        <v>3236.841046</v>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>2026-10-08T14:50:09-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F347"/>
+  <dimension ref="A1:F348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10840,6 +10840,36 @@
         </is>
       </c>
     </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D348" t="n">
+        <v>3236.417658</v>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>2026-10-09T14:27:30-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/dollar_daily.xlsx
+++ b/data/output/dollar_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F348"/>
+  <dimension ref="A1:F349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10870,6 +10870,36 @@
         </is>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D349" t="n">
+        <v>3236.568377</v>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>exchangerate.host</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>2026-10-10T13:28:06-05:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
